--- a/threeKingdomSlayer/Locus/knowledge/plan/first-level-difficulty-20261025-v2.xlsx
+++ b/threeKingdomSlayer/Locus/knowledge/plan/first-level-difficulty-20261025-v2.xlsx
@@ -585,10 +585,10 @@
         <v>7</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46.3</v>
+        <v>60.8</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>5760</v>
+        <v>8880</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -597,12 +597,12 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>第0条战斗是开发用 Test_Node_Battle（血×0.25/伤害×0.15），正式战斗排在第1条</t>
+          <t>已落 5 波（摊在纵深、每排 1~2 只）；开发用 Test_Node_Battle 已从 Node_N1 删除</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>删掉第0条开发战斗（待办 D1-4）</t>
+          <t>保持；用机器人量清场时长再拧 hp×</t>
         </is>
       </c>
     </row>
@@ -638,10 +638,10 @@
         <v>13</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>57.7</v>
+        <v>63.2</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>8355</v>
+        <v>10205</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -650,12 +650,12 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>教学台词按波次配：wave3=破盾、wave4=骑将；但第1波是 1011、第2波才有 1021+109 → 台词与波次错位</t>
+          <t>已落 5 波：1021 在第0波、109 在第1波 → 与教学台词顺序对上</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>按建议：1021 放第0波、109 放第1波，台词即可对上</t>
+          <t>保持；用机器人量清场时长再拧 hp×</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>纯过场/分叉｜不打</t>
+          <t>纯过场/分叉｜不打（**2026-10-25 已接上右路出口 j1_to_n2**）</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -691,7 +691,7 @@
         <v>13</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>57.7</v>
+        <v>63.2</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>0</v>
@@ -744,7 +744,7 @@
         <v>13</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>57.7</v>
+        <v>63.2</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>0</v>
@@ -797,10 +797,10 @@
         <v>21</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>17276</v>
+        <v>17285</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -809,12 +809,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>只有 2 波，且 1021/109/1011 全挤在第0排（正面），没有远程、没有 Boss</t>
+          <t>已落 6 波：105 后排远程 + 盾兵掩护 + 104 Boss（×7.5）在最后一排</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>按建议改成 6 波：105 后排 + 盾兵掩护 + Boss 收尾</t>
+          <t>用机器人量清场时长再拧 hp×</t>
         </is>
       </c>
     </row>
@@ -850,10 +850,10 @@
         <v>28</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>86.2</v>
+        <v>69.2</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>21577</v>
+        <v>18602</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -862,12 +862,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1 波 10 排 8 只，且血/攻速/伤害全 ×0.1（占位配置）</t>
+          <t>已落 6 波：倍率从 ×0.1 占位改为按成长重算；终局 104 ×11.5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>按建议改成 6 波，倍率按玩家成长重算</t>
+          <t>用机器人量清场时长再拧 hp×</t>
         </is>
       </c>
     </row>
@@ -903,10 +903,10 @@
         <v>28</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>86.2</v>
+        <v>69.2</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>52968</v>
+        <v>54972</v>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:T25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -947,15 +947,17 @@
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
     <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="44" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="44" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1001,50 +1003,60 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>建议hp×</t>
+          <t>推导hp×</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>已落hp×</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>实测清场(s)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>建议总HP</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>建议spd×</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>建议dmg×</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>建议bossHp×</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>本波经验</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>目标清场</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>预计清场</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>铁律自检</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
@@ -1076,47 +1088,53 @@
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>34.9</v>
+        <v>58.4</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>400</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>920</v>
+        <v>3.6</v>
       </c>
       <c r="K2" s="2" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>1520</v>
+      </c>
+      <c r="M2" s="2" t="n">
         <v>0.85</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="N2" s="2" t="n">
         <v>0.45</v>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="P2" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>26s</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>26s</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>清场26s✔</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>第1波：两只并排，认识「一列 = 几个敌人」</t>
         </is>
@@ -1148,49 +1166,55 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>34.9</v>
+        <v>58.4</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>600</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>960</v>
+        <v>2.7</v>
       </c>
       <c r="K3" s="2" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>1620</v>
+      </c>
+      <c r="M3" s="2" t="n">
         <v>0.85</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="N3" s="2" t="n">
         <v>0.45</v>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="P3" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="Q3" s="2" t="inlineStr">
         <is>
           <t>28s</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="R3" s="2" t="inlineStr">
         <is>
           <t>28s</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>清场28s✔</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>第2波：三只一排，学会用范围技</t>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>第2波：三只一排，学会用范围技（斩击打整排）</t>
         </is>
       </c>
     </row>
@@ -1220,47 +1244,53 @@
         <v>2</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>36.8</v>
+        <v>58.8</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>600</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1080</v>
+        <v>3</v>
       </c>
       <c r="K4" s="2" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>1740</v>
+      </c>
+      <c r="M4" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="N4" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="P4" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>30s</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>29s</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>清场29s✔</t>
-        </is>
-      </c>
       <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>30s</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>清场30s✔</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>第3波：前后两排，要换目标</t>
         </is>
@@ -1277,7 +1307,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>row0: 1011+1011；row2: 1011+1011+1011</t>
+          <t>row0: 1011+1011；row2: 1011+1011；row4: 1011</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1292,49 +1322,55 @@
         <v>4</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>40.6</v>
+        <v>59.6</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1000</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1300</v>
+        <v>1.9</v>
       </c>
       <c r="K5" s="2" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M5" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="N5" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="P5" s="2" t="n">
         <v>400</v>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>32s</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>32s</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>清场32s✔</t>
         </is>
       </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>第4波：压力上来</t>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>第4波：三排纵深，每排 1~2 只</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1385,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>row0: 1011+1011+1011；row2: 1011+1011</t>
+          <t>row0: 1011+1011；row1: 1011+1011；row2: 1011</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1364,49 +1400,55 @@
         <v>6</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>44.4</v>
+        <v>60.4</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1000</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1500</v>
+        <v>2</v>
       </c>
       <c r="K6" s="2" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>2100</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="N6" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="P6" s="2" t="n">
         <v>400</v>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>34s</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>34s</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>清场34s✔</t>
-        </is>
-      </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>第5波：N1 收尾，两排夹击</t>
+          <t>35s</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>清场35s✔</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>第5波：N1 收尾，排距收紧</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1463,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>row0: 1021；row1: 1011+1011</t>
+          <t>row0: 1021；row2: 1011+1011</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1436,47 +1478,53 @@
         <v>7</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46.3</v>
+        <v>60.8</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>550</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1375</v>
+        <v>3.4</v>
       </c>
       <c r="K7" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>1815</v>
+      </c>
+      <c r="M7" s="2" t="n">
         <v>0.85</v>
       </c>
-      <c r="L7" s="2" t="n">
+      <c r="N7" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="P7" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>30s</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>30s</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>清场30s✔</t>
         </is>
       </c>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
         <is>
           <t>**必须第0波**：对教学台词 tutorial_t0_wave3（蓄力上挑破盾）</t>
         </is>
@@ -1493,7 +1541,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>row0: 109；row1: 1011+1011</t>
+          <t>row0: 109；row2: 1011+1011</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1508,47 +1556,53 @@
         <v>8</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>48.2</v>
+        <v>61.2</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>900</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1620</v>
+        <v>2.4</v>
       </c>
       <c r="K8" s="2" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>2070</v>
+      </c>
+      <c r="M8" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="N8" s="2" t="n">
         <v>0.55</v>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="P8" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>34s</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>34s</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>清场34s✔</t>
         </is>
       </c>
-      <c r="R8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
         <is>
           <t>**必须第1波**：对教学台词 tutorial_t0_wave4（骑将登场）</t>
         </is>
@@ -1565,7 +1619,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>row0: 1011+1011+1011</t>
+          <t>row0: 1011+1011；row2: 1011</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1580,47 +1634,53 @@
         <v>9</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>50.1</v>
+        <v>61.6</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>600</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1620</v>
+        <v>3.2</v>
       </c>
       <c r="K9" s="2" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>1980</v>
+      </c>
+      <c r="M9" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="L9" s="2" t="n">
+      <c r="N9" s="2" t="n">
         <v>0.55</v>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N9" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>32s</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>32s</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>清场32s✔</t>
         </is>
       </c>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
         <is>
           <t>第3波：纯 1011，让玩家缓口气</t>
         </is>
@@ -1652,47 +1712,53 @@
         <v>10</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>550</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1760</v>
+        <v>3.7</v>
       </c>
       <c r="K10" s="2" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>2090</v>
+      </c>
+      <c r="M10" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="L10" s="2" t="n">
+      <c r="N10" s="2" t="n">
         <v>0.55</v>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N10" s="2" t="n">
+      <c r="P10" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>34s</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>34s</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>清场34s✔</t>
         </is>
       </c>
-      <c r="R10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
         <is>
           <t>第4波：第二只盾兵</t>
         </is>
@@ -1709,7 +1775,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>row0: 1021+1021；row2: 1011+1011+1011</t>
+          <t>row0: 1021+1021；row2: 1011+1011；row4: 1011</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1724,47 +1790,53 @@
         <v>11</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>53.9</v>
+        <v>62.4</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>900</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1980</v>
+        <v>2.8</v>
       </c>
       <c r="K11" s="2" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>2250</v>
+      </c>
+      <c r="M11" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="L11" s="2" t="n">
+      <c r="N11" s="2" t="n">
         <v>0.6</v>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N11" s="2" t="n">
+      <c r="P11" s="2" t="n">
         <v>340</v>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>36s</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>37s</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>清场37s✔</t>
-        </is>
-      </c>
       <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>36s</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>清场36s✔</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
         <is>
           <t>第5波：双盾压阵，E0 收尾</t>
         </is>
@@ -1796,7 +1868,7 @@
         <v>13</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>57.7</v>
+        <v>63.2</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>0</v>
@@ -1807,32 +1879,40 @@
       <c r="J12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="2" t="n">
-        <v>0</v>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="M12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
           <t>0s</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0s</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr">
         <is>
           <t>分叉节点，不打（现状正确）</t>
         </is>
@@ -1864,7 +1944,7 @@
         <v>13</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>57.7</v>
+        <v>63.2</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>0</v>
@@ -1875,32 +1955,40 @@
       <c r="J13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="2" t="n">
-        <v>0</v>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="M13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>0s</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>0s</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr">
         <is>
           <t>村落外围不打（现状正确）；要加伏击就 1 波 1011×3 + 105×1</t>
         </is>
@@ -1917,7 +2005,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>row0: 1011+1011+1011；row3: 105</t>
+          <t>row0: 1011+1011；row1: 1011；row3: 105</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1932,47 +2020,53 @@
         <v>13</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>57.7</v>
+        <v>63.2</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>608</v>
+        <v>640</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1824</v>
+        <v>2.6</v>
       </c>
       <c r="K14" s="2" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>2048</v>
+      </c>
+      <c r="M14" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="L14" s="2" t="n">
+      <c r="N14" s="2" t="n">
         <v>0.6</v>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N14" s="2" t="n">
+      <c r="P14" s="2" t="n">
         <v>290</v>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>32s</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>32s</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>远程后排✔ 清场32s✔</t>
         </is>
       </c>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
         <is>
           <t>首次出现远程：105 放最后排（射程3），前排 1011 当掩体</t>
         </is>
@@ -2004,47 +2098,53 @@
         <v>14</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>59.6</v>
+        <v>63.6</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>416</v>
+        <v>480</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>2038</v>
+        <v>4.1</v>
       </c>
       <c r="K15" s="2" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>2160</v>
+      </c>
+      <c r="M15" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="L15" s="2" t="n">
+      <c r="N15" s="2" t="n">
         <v>0.6</v>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N15" s="2" t="n">
+      <c r="P15" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>34s</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>34s</t>
         </is>
       </c>
-      <c r="Q15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>远程后排✔ 清场34s✔</t>
         </is>
       </c>
-      <c r="R15" s="2" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr">
         <is>
           <t>两只 105 同排，逼范围技或突进</t>
         </is>
@@ -2061,7 +2161,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>row0: 1011+1011+1011；row1: 1021</t>
+          <t>row0: 1011+1011；row1: 1011+1021</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2076,47 +2176,53 @@
         <v>15</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>61.5</v>
+        <v>64</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>750</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>2250</v>
+        <v>3.2</v>
       </c>
       <c r="K16" s="2" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>2325</v>
+      </c>
+      <c r="M16" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="L16" s="2" t="n">
+      <c r="N16" s="2" t="n">
         <v>0.6</v>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N16" s="2" t="n">
+      <c r="P16" s="2" t="n">
         <v>290</v>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>36s</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>37s</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>清场37s✔</t>
-        </is>
-      </c>
       <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>36s</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>清场36s✔</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
         <is>
           <t>盾兵正式登场（前面已教过破盾）</t>
         </is>
@@ -2148,47 +2254,55 @@
         <v>16</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>63.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>566</v>
+        <v>630</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2434</v>
-      </c>
-      <c r="K17" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>2457</v>
+      </c>
+      <c r="M17" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="L17" s="2" t="n">
+      <c r="N17" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N17" s="2" t="n">
+      <c r="P17" s="2" t="n">
         <v>310</v>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>38s</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>38s</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>远程后排✔ 清场38s✔</t>
         </is>
       </c>
-      <c r="R17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
         <is>
           <t>**盾兵掩护弓兵**：1021 在 row0 吃伤害，105 在 row2 输出</t>
         </is>
@@ -2205,7 +2319,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>row0: 109；row1: 1011+1011+1011</t>
+          <t>row0: 109；row1: 1011+1011；row2: 1011</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2220,7 +2334,7 @@
         <v>17</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>65.3</v>
+        <v>64.8</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>1100</v>
@@ -2229,38 +2343,46 @@
         <v>2.4</v>
       </c>
       <c r="J18" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
         <v>2640</v>
       </c>
-      <c r="K18" s="2" t="n">
+      <c r="M18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L18" s="2" t="n">
+      <c r="N18" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N18" s="2" t="n">
+      <c r="P18" s="2" t="n">
         <v>340</v>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>40s</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>40s</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>清场40s✔</t>
-        </is>
-      </c>
       <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>41s</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>清场41s✔</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
         <is>
           <t>骑兵冲锋高潮波</t>
         </is>
@@ -2277,7 +2399,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>row0: 1011+1011+1011；row4: 104</t>
+          <t>row0: 1011+1011；row2: 1011；row4: 104</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2292,45 +2414,53 @@
         <v>18</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>67.2</v>
+        <v>65.2</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>4350</v>
       </c>
       <c r="I19" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J19" s="2" t="n">
         <v>1.4</v>
       </c>
-      <c r="J19" s="2" t="n">
-        <v>6090</v>
-      </c>
-      <c r="K19" s="2" t="n">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>5655</v>
+      </c>
+      <c r="M19" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="2" t="n">
+      <c r="N19" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="M19" s="2" t="n">
+      <c r="O19" s="2" t="n">
         <v>7.5</v>
       </c>
-      <c r="N19" s="2" t="n">
+      <c r="P19" s="2" t="n">
         <v>640</v>
       </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>88s</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>91s</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>Boss在最后排✔ 清场91s✔</t>
-        </is>
-      </c>
       <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>87s</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>Boss在最后排✔ 清场87s✔</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
         <is>
           <t>**Boss 波：104 必须在最后一排**（铁律九）</t>
         </is>
@@ -2347,7 +2477,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>row0: 1011+1011+1011</t>
+          <t>row0: 1011+1011；row2: 1011</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2362,47 +2492,53 @@
         <v>21</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>600</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2460</v>
+        <v>3.3</v>
       </c>
       <c r="K20" s="2" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>2280</v>
+      </c>
+      <c r="M20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L20" s="2" t="n">
+      <c r="N20" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N20" s="2" t="n">
+      <c r="P20" s="2" t="n">
         <v>240</v>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>34s</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>34s</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>清场34s✔</t>
         </is>
       </c>
-      <c r="R20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
         <is>
           <t>巷战开局：数量低但节奏快</t>
         </is>
@@ -2434,47 +2570,53 @@
         <v>22</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>74.8</v>
+        <v>66.8</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>408</v>
+        <v>440</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2693</v>
+        <v>5</v>
       </c>
       <c r="K21" s="2" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>2420</v>
+      </c>
+      <c r="M21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L21" s="2" t="n">
+      <c r="N21" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N21" s="2" t="n">
+      <c r="P21" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>36s</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>36s</t>
         </is>
       </c>
-      <c r="Q21" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>远程后排✔ 清场36s✔</t>
         </is>
       </c>
-      <c r="R21" s="2" t="inlineStr">
+      <c r="T21" s="2" t="inlineStr">
         <is>
           <t>远程压制</t>
         </is>
@@ -2491,7 +2633,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>row0: 1011+1011+1011；row1: 1021</t>
+          <t>row0: 1011+1011；row1: 1011+1021</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2506,47 +2648,53 @@
         <v>22</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>74.8</v>
+        <v>66.8</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>750</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2850</v>
+        <v>3.4</v>
       </c>
       <c r="K22" s="2" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>2550</v>
+      </c>
+      <c r="M22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L22" s="2" t="n">
+      <c r="N22" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N22" s="2" t="n">
+      <c r="P22" s="2" t="n">
         <v>290</v>
       </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>38s</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>38s</t>
         </is>
       </c>
-      <c r="Q22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>清场38s✔</t>
         </is>
       </c>
-      <c r="R22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
         <is>
           <t>盾兵压阵</t>
         </is>
@@ -2563,7 +2711,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>row0: 1011+1011；row1: 109；row2: 105+105+105</t>
+          <t>row0: 1011+1011；row1: 109；row2: 105+105；row4: 105</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2578,47 +2726,55 @@
         <v>23</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>76.7</v>
+        <v>67.2</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>924</v>
+        <v>1020</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>3049</v>
-      </c>
-      <c r="K23" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>2652</v>
+      </c>
+      <c r="M23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L23" s="2" t="n">
+      <c r="N23" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N23" s="2" t="n">
+      <c r="P23" s="2" t="n">
         <v>410</v>
       </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>40s</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>40s</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>远程后排✔ 清场40s✔</t>
-        </is>
-      </c>
       <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>39s</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>远程后排✔ 清场39s✔</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
         <is>
           <t>全机制同场：骑兵 + 三只弓兵</t>
         </is>
@@ -2635,7 +2791,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>row0: 1021；row1: 1011+1011+1011</t>
+          <t>row0: 1021；row1: 1011+1011；row3: 1011</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2650,47 +2806,55 @@
         <v>25</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>80.5</v>
+        <v>68</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>750</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>3375</v>
-      </c>
-      <c r="K24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>2850</v>
+      </c>
+      <c r="M24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L24" s="2" t="n">
+      <c r="N24" s="2" t="n">
         <v>0.7</v>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N24" s="2" t="n">
+      <c r="P24" s="2" t="n">
         <v>290</v>
       </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>42s</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>42s</t>
         </is>
       </c>
-      <c r="Q24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
         <is>
           <t>清场42s✔</t>
         </is>
       </c>
-      <c r="R24" s="2" t="inlineStr">
+      <c r="T24" s="2" t="inlineStr">
         <is>
           <t>盾兵护住后排</t>
         </is>
@@ -2722,45 +2886,53 @@
         <v>26</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>82.40000000000001</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>6500</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>7150</v>
-      </c>
-      <c r="K25" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="L25" s="2" t="n">
+        <v>5850</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" s="2" t="n">
         <v>0.7</v>
       </c>
-      <c r="M25" s="2" t="n">
+      <c r="O25" s="2" t="n">
         <v>11.5</v>
       </c>
-      <c r="N25" s="2" t="n">
+      <c r="P25" s="2" t="n">
         <v>690</v>
       </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>87s</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>87s</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>Boss在最后排✔ 清场87s✔</t>
-        </is>
-      </c>
       <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>86s</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>Boss在最后排✔ 清场86s✔</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
         <is>
           <t>**终局 Boss**：104 最后一排；盾兵护 Boss</t>
         </is>
@@ -2882,7 +3054,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>波次的承伤与经验来源；单波 3~4 只（不做大量对怪）</t>
+          <t>波次的承伤与经验来源；单波 3~5 只（不做大量对怪）</t>
         </is>
       </c>
     </row>
@@ -2982,7 +3154,7 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>5</v>
@@ -3003,12 +3175,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>射程 3 的随机轨迹远程；后排火力</t>
+          <t>射程 3 的随机轨迹远程；后排火力（40 血 ≈ 两下平A）</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>必须放后 50% 排；本体一戳就死，威胁来自射程3的箭</t>
+          <t>必须放后 50% 排；8 血已改为 40 血（2026-10-25），威胁来自射程3的箭而不是被一戳秒</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3234,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>以上为 prefab 实测值（2026-10-25）。与 design/numerical-balance-draft.md §1.2 的旧表不一致：1011 实测 200HP/3攻（文档写 16HP/10攻）、105 实测 8HP、104 实测 500HP/400经验 → 数值表以资产为准。</t>
+          <t>以上为 prefab 实测值（2026-10-25）。与 design/numerical-balance-draft.md §1.2 的旧表不一致：1011 实测 200HP/3攻（文档写 16HP/10攻）、105 实测 40HP（本轮从 8HP 调上来）、104 实测 500HP/400经验 → 数值表以资产为准。</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
@@ -3161,10 +3333,10 @@
         <v>7</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46.3</v>
+        <v>60.8</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>5760</v>
+        <v>8880</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -3193,10 +3365,10 @@
         <v>13</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>57.7</v>
+        <v>63.2</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>8355</v>
+        <v>10205</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -3225,7 +3397,7 @@
         <v>13</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>57.7</v>
+        <v>63.2</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0</v>
@@ -3257,7 +3429,7 @@
         <v>13</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>57.7</v>
+        <v>63.2</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0</v>
@@ -3289,10 +3461,10 @@
         <v>21</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>17276</v>
+        <v>17285</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -3321,10 +3493,10 @@
         <v>28</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>86.2</v>
+        <v>69.2</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>21577</v>
+        <v>18602</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -3888,7 +4060,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>N2 第4波 / N3 第5波</t>
+          <t>N2 第4波 / N3 第6波（Boss 波）</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -3915,7 +4087,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>E0 第1波、N2 第5波、N3 第4波</t>
+          <t>E0 第2波、N2 第5波、N3 第4波</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -3937,7 +4109,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>射程 3、本体 8 血一戳就死；威胁来自箭不是血</t>
+          <t>射程 3、本体 40 血（两下平A）；威胁来自箭不是血</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -4023,12 +4195,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>按「DPS×目标秒数÷基础HP」逐波反推</t>
+          <t>**2026-10-25 改用实测 DPS**（旧公式 33+1.9×等级 是假设，偏大；机器人实测有效 DPS 只有 50~72）</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>波次明细：建议总HP ÷ DPS = 目标清场</t>
+          <t>波次明细：推导hp× / 已落hp× 两列</t>
         </is>
       </c>
     </row>
@@ -4077,7 +4249,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>N1→N3 hp× 从 ~1.5 抬到 ~4</t>
+          <t>N1→N3 hp× 从 ~1.5 抬到 ~4（105 加血后远程波另算）</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -4185,7 +4357,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>波次明细「预计清场」列</t>
+          <t>波次明细「预计清场」列（待机器人实测替换）</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -4259,7 +4431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4307,7 +4479,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>经验产出 6960 vs 目标 11172；方案 A/B/C 见「玩家成长」页</t>
+          <t>经验产出 6960 vs 目标 11172；方案 A/B/C 见「玩家成长」页。2026-10-25 决定：先按方案 A 落表，机器人量完再定。</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -4327,17 +4499,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>104 放哪条支路</t>
+          <t>104 放在哪条支路</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>本表暂定：N2 用 ×7.5、N3 用 ×11.5（同一 prefab，阶段数相同）</t>
+          <t>2026-10-25 已定：两条都放（N2 ×7.5 / N3 ×11.5）</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>你拍板（对应 Q3）</t>
+          <t>已定</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -4357,12 +4529,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>现状还在，正式战斗排第1条</t>
+          <t>2026-10-25 已删（Node_N1 只剩 Formal_N1_Battle）</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>你拍板（D1-4）</t>
+          <t>已定</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -4382,12 +4554,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>现状第1波是 1011、第2波才有 1021+109 → 台词错位</t>
+          <t>2026-10-25 已改：1021 第0波、109 第1波</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>确认按本表调整</t>
+          <t>已定</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -4407,12 +4579,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>血/攻速/伤害全 ×0.1</t>
+          <t>2026-10-25 已改为 6 波 + 重算倍率</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>按本表落配置后实机验证</t>
+          <t>已定</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -4432,12 +4604,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>本表所有 hp× 都按它反推</t>
+          <t>本表所有 hp× 都按它反推；机器人实测后要替换</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>实机打一遍替换</t>
+          <t>机器人实测后回填</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -4457,12 +4629,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>一戳就死，威胁全在射程3；后排压力≈0</t>
+          <t>2026-10-25 已提到 40 血</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>是否给弓兵加血</t>
+          <t>已定</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -4507,7 +4679,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>本表按 N1 5 / E0 6 / J1 1 / EV 2 / N2 7 / N3 8 分钟估</t>
+          <t>本表按 N1 5 / E0 6 / J1 1 / EV 2 / N2 7 / N3 8 分钟估；与「一次循环 ≤15min」冲突，待实测</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -4518,6 +4690,31 @@
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>经验曲线与升级节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>玩家复活次数</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>资产 Hero_Zhangfei 实测 reviveCount=0（100 血），文档写 3；2026-10-25 决定保持 0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>已定（保持 0）</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Boss 墙的容错</t>
         </is>
       </c>
     </row>
@@ -4580,17 +4777,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Stab 20伤/0.3s = 66 DPS（数值草案按 10伤算的 33 DPS，资产里是 20，翻倍）；Slash 20伤/0.65s = 31 DPS；Stab 还能点哪打哪</t>
+          <t>Stab 20伤/0.3s = 66 DPS（数值草案按 10伤算的 33 DPS，资产里是 20，翻倍）；Slash 20伤/0.65s = 31 DPS。**实测校正**：Zhangfei_Slash 的 rangeRows=1（只打当前前排那一排），「Slash 一次 3 排」需要 attack_range_boost 升级（+1 排/级，但伤害 -30%/-25%）。</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>玩家只要平A；Slash 只有在「一列 3 只以上」时划算，而「不做大量对怪」恰好消灭了这个场景</t>
+          <t>玩家只要平A；Slash 的价值取决于「前排同时站了几只」，而不是「一列有几只」</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>①「少量对怪」≠「一排多只」：把敌人摊在纵深（每排 1~2 只、纵深 2~3 排）→ Stab 一次只打 1 只、Slash 一次 3 排 → Slash DPS×3=93 &gt; Stab 66 ✓ 总数不变</t>
+          <t>① 敌人摊在纵深后，前排变薄 → 斩击打不到人（**别把摊纵深当成给 Slash 创造机会**）；② 想让范围技有存在空间，要么让前排保持 2~3 只，要么给斩击单独加「跨排」；③ 本轮落地：N1 第2波保留「前排 3 只」当范围技教学，其余波次每排 1~2 只</t>
         </is>
       </c>
     </row>
@@ -4605,7 +4802,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>105 弓兵只有 8 血（Stab 一下秒杀）→ 来不及射第二箭 → 远程压力=0；射程 3 这个「必须处理」的信号被 8 血抹掉了</t>
+          <t>105 弓兵原本只有 8 血（Stab 一下秒杀）→ 来不及射第二箭 → 远程压力=0；射程 3 这个「必须处理」的信号被 8 血抹掉了。**2026-10-25 已把 105 调到 40 血**（两下平A），并把 105 与杂兵同波、固定后排。</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -4717,7 +4914,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>N1 的波次从「row0 三只一排」改成「每排 1~2 只、纵深 2~3 排」；每波加 1 个「门」；105 与杂兵同波且固定后排。</t>
+          <t>已落（2026-10-25）：N1/E0/N2/N3 共 22 波，每排 ≤2 只（N1 第2波「前排 3 只」是范围技教学）；每波至少 1 个「门」（1021 格挡 / 105 后排远程 / 109 冲锋）；105 与杂兵同波且固定后排；104 Boss 两条支路都放（N2 ×7.5 / N3 ×11.5）。</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>

--- a/threeKingdomSlayer/Locus/knowledge/plan/first-level-difficulty-20261025-v2.xlsx
+++ b/threeKingdomSlayer/Locus/knowledge/plan/first-level-difficulty-20261025-v2.xlsx
@@ -588,11 +588,11 @@
         <v>60.8</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8880</v>
+        <v>2020</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>150s</t>
+          <t>35s</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -641,11 +641,11 @@
         <v>63.2</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>10205</v>
+        <v>2705</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>166s</t>
+          <t>43s</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -800,11 +800,11 @@
         <v>66.40000000000001</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>17285</v>
+        <v>7425</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>268s</t>
+          <t>115s</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -853,11 +853,11 @@
         <v>69.2</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>18602</v>
+        <v>9270</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>277s</t>
+          <t>135s</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -906,11 +906,11 @@
         <v>69.2</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>54972</v>
+        <v>21420</v>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>861s</t>
+          <t>328s</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -1094,16 +1094,16 @@
         <v>400</v>
       </c>
       <c r="I2" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K2" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="J2" s="2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>25.4</v>
-      </c>
       <c r="L2" s="2" t="n">
-        <v>1520</v>
+        <v>240</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>0.85</v>
@@ -1121,17 +1121,17 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>26s</t>
+          <t>4s</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>26s</t>
+          <t>4s</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>清场26s✔</t>
+          <t>清场4s⚠</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
@@ -1172,16 +1172,16 @@
         <v>600</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>30.3</v>
+        <v>5.8</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>1620</v>
+        <v>360</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>0.85</v>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>28s</t>
+          <t>6s</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>28s</t>
+          <t>6s</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>清场28s✔</t>
+          <t>清场6s⚠</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
@@ -1250,16 +1250,16 @@
         <v>600</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3</v>
+        <v>0.52</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>34.8</v>
+        <v>6.5</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1740</v>
+        <v>420</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>0.9</v>
@@ -1277,17 +1277,17 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>30s</t>
+          <t>7s</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>30s</t>
+          <t>7s</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>清场30s✔</t>
+          <t>清场7s⚠</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -1328,16 +1328,16 @@
         <v>1000</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.9</v>
+        <v>0.52</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>30.1</v>
+        <v>9.4</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>1900</v>
+        <v>500</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>0.9</v>
@@ -1355,17 +1355,17 @@
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>32s</t>
+          <t>9s</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>32s</t>
+          <t>8s</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>清场32s✔</t>
+          <t>清场8s⚠</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -1406,16 +1406,16 @@
         <v>1000</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2</v>
+        <v>0.54</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>36.4</v>
+        <v>9.1</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>2100</v>
+        <v>500</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>0.9</v>
@@ -1433,17 +1433,17 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>34s</t>
+          <t>9s</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>35s</t>
+          <t>8s</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>清场35s✔</t>
+          <t>清场8s⚠</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -1484,16 +1484,16 @@
         <v>550</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>3.4</v>
+        <v>0.55</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>32</v>
+        <v>7.6</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>1815</v>
+        <v>495</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>0.85</v>
@@ -1511,17 +1511,17 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>30s</t>
+          <t>8s</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>30s</t>
+          <t>8s</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>清场30s✔</t>
+          <t>清场8s⚠</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1562,16 +1562,16 @@
         <v>900</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2.4</v>
+        <v>0.55</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>38.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>2070</v>
+        <v>630</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>0.9</v>
@@ -1589,17 +1589,17 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>34s</t>
+          <t>10s</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>34s</t>
+          <t>10s</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>清场34s✔</t>
+          <t>清场10s⚠</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1640,16 +1640,16 @@
         <v>600</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>3.2</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>32.7</v>
+        <v>7.3</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>1980</v>
+        <v>420</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>0.9</v>
@@ -1667,17 +1667,17 @@
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>32s</t>
+          <t>7s</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>32s</t>
+          <t>7s</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>清场32s✔</t>
+          <t>清场7s⚠</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
@@ -1718,16 +1718,16 @@
         <v>550</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3.7</v>
+        <v>0.57</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>34.2</v>
+        <v>6.8</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>2090</v>
+        <v>440</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>0.9</v>
@@ -1745,17 +1745,17 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>34s</t>
+          <t>7s</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>34s</t>
+          <t>7s</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>清场34s✔</t>
+          <t>清场7s⚠</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1796,16 +1796,16 @@
         <v>900</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.8</v>
+        <v>0.58</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>37.5</v>
+        <v>11</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>2250</v>
+        <v>720</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>0.95</v>
@@ -1823,17 +1823,17 @@
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>36s</t>
+          <t>11s</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>36s</t>
+          <t>12s</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>清场36s✔</t>
+          <t>清场12s⚠</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -2023,19 +2023,21 @@
         <v>63.2</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>640</v>
+        <v>800</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>36.1</v>
+        <v>0.58</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>2048</v>
+        <v>480</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>0.95</v>
@@ -2053,17 +2055,17 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>32s</t>
+          <t>7s</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>32s</t>
+          <t>8s</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>远程后排✔ 清场32s✔</t>
+          <t>远程后排✔ 清场8s⚠</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -2101,19 +2103,21 @@
         <v>63.6</v>
       </c>
       <c r="H15" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
         <v>480</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>2160</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>0.95</v>
@@ -2131,17 +2135,17 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>34s</t>
+          <t>7s</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>34s</t>
+          <t>8s</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>远程后排✔ 清场34s✔</t>
+          <t>远程后排✔ 清场8s⚠</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
@@ -2182,16 +2186,18 @@
         <v>750</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>34.2</v>
+        <v>0.59</v>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>2325</v>
+        <v>450</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>0.95</v>
@@ -2209,17 +2215,17 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>36s</t>
+          <t>7s</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>36s</t>
+          <t>7s</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>清场36s✔</t>
+          <t>清场7s⚠</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2257,13 +2263,13 @@
         <v>64.40000000000001</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>630</v>
+        <v>950</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>3.1</v>
+        <v>0.59</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
@@ -2271,7 +2277,7 @@
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>2457</v>
+        <v>570</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>0.95</v>
@@ -2289,17 +2295,17 @@
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>38s</t>
+          <t>9s</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>38s</t>
+          <t>9s</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>远程后排✔ 清场38s✔</t>
+          <t>远程后排✔ 清场9s⚠</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2340,10 +2346,10 @@
         <v>1100</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -2351,7 +2357,7 @@
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>2640</v>
+        <v>660</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>1</v>
@@ -2369,17 +2375,17 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>40s</t>
+          <t>10s</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>41s</t>
+          <t>10s</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>清场41s✔</t>
+          <t>清场10s⚠</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
@@ -2420,10 +2426,10 @@
         <v>4350</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
@@ -2431,7 +2437,7 @@
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>5655</v>
+        <v>4785</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>1</v>
@@ -2447,17 +2453,17 @@
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>88s</t>
+          <t>75s</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>87s</t>
+          <t>73s</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>Boss在最后排✔ 清场87s✔</t>
+          <t>Boss在最后排✔ 清场73s✔</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -2498,16 +2504,16 @@
         <v>600</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>37.8</v>
+        <v>7.7</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>2280</v>
+        <v>540</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>1</v>
@@ -2525,17 +2531,17 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>34s</t>
+          <t>8s</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>34s</t>
+          <t>8s</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>清场34s✔</t>
+          <t>清场8s⚠</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2573,19 +2579,19 @@
         <v>66.8</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>440</v>
+        <v>600</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>39.1</v>
+        <v>7.2</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>2420</v>
+        <v>480</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>1</v>
@@ -2603,17 +2609,17 @@
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>36s</t>
+          <t>7s</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>36s</t>
+          <t>7s</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>远程后排✔ 清场36s✔</t>
+          <t>远程后排✔ 清场7s⚠</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
@@ -2654,16 +2660,16 @@
         <v>750</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>3.4</v>
+        <v>0.61</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>40.4</v>
+        <v>11.8</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>2550</v>
+        <v>825</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>1</v>
@@ -2681,17 +2687,17 @@
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>38s</t>
+          <t>12s</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>38s</t>
+          <t>12s</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>清场38s✔</t>
+          <t>清场12s⚠</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -2729,21 +2735,19 @@
         <v>67.2</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>1020</v>
+        <v>1500</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.61</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>21</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>2652</v>
+        <v>1350</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>1</v>
@@ -2761,17 +2765,17 @@
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>40s</t>
+          <t>21s</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>39s</t>
+          <t>20s</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>远程后排✔ 清场39s✔</t>
+          <t>远程后排✔ 清场20s⚠</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2812,18 +2816,16 @@
         <v>750</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.62</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>11.7</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>2850</v>
+        <v>825</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>1</v>
@@ -2841,17 +2843,17 @@
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>42s</t>
+          <t>12s</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>42s</t>
+          <t>12s</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>清场42s✔</t>
+          <t>清场12s⚠</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
@@ -2889,13 +2891,13 @@
         <v>68.40000000000001</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>6500</v>
+        <v>5250</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1</v>
+        <v>0.62</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -2903,7 +2905,7 @@
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>5850</v>
+        <v>5250</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>1</v>
@@ -2912,24 +2914,24 @@
         <v>0.7</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="P25" s="2" t="n">
         <v>690</v>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>87s</t>
+          <t>75s</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>86s</t>
+          <t>77s</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>Boss在最后排✔ 清场86s✔</t>
+          <t>Boss在最后排✔ 清场77s✔</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -3154,7 +3156,7 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>5</v>
@@ -3175,12 +3177,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>射程 3 的随机轨迹远程；后排火力（40 血 ≈ 两下平A）</t>
+          <t>射程 3 的随机轨迹远程；后排火力（200 血 ≈ 3 段 jab）</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>必须放后 50% 排；8 血已改为 40 血（2026-10-25），威胁来自射程3的箭而不是被一戳秒</t>
+          <t>必须放后 50% 排；40 血已改为 200 血（2026-10-25）→ 与 1011 同档，≈3 段 jab，不会被一戳秒</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3236,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>以上为 prefab 实测值（2026-10-25）。与 design/numerical-balance-draft.md §1.2 的旧表不一致：1011 实测 200HP/3攻（文档写 16HP/10攻）、105 实测 40HP（本轮从 8HP 调上来）、104 实测 500HP/400经验 → 数值表以资产为准。</t>
+          <t>以上为 prefab 实测值（2026-10-25）。与 design/numerical-balance-draft.md §1.2 的旧表不一致：1011 实测 200HP/3攻（文档写 16HP/10攻）、105 实测 200HP（本轮 40→200）、104 实测 500HP/400经验 → 数值表以资产为准。</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
@@ -3336,7 +3338,7 @@
         <v>60.8</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>8880</v>
+        <v>2020</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -3368,7 +3370,7 @@
         <v>63.2</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>10205</v>
+        <v>2705</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -3464,7 +3466,7 @@
         <v>66.40000000000001</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>17285</v>
+        <v>7425</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -3496,7 +3498,7 @@
         <v>69.2</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>18602</v>
+        <v>9270</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -4190,7 +4192,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>倍率递增幅度逐波加大，不等距</t>
+          <t>倍率随玩家成长递增（实测 DPS 57→70）</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -4249,7 +4251,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>N1→N3 hp× 从 ~1.5 抬到 ~4（105 加血后远程波另算）</t>
+          <t>N1 0.50 → N3 0.62（1011 有效血 100→124 ≈ 3~4 段 jab）</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -4276,7 +4278,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>N2 104 → ×7.5；N3 104 → ×11.5</t>
+          <t>N2 104 → ×7.5（3750）；N3 104 → ×9（4500）</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -4347,17 +4349,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>单波清场 30~55 秒</t>
+          <t>单波清场时长</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>普通波 30~55s，Boss 波 45~90s</t>
+          <t>**2026-10-25 改口径**：杂兵 3 段 jab 能杀 → 普通波 4~12s（不是旧表的 30~55s）；Boss 波 45~90s</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>波次明细「预计清场」列（待机器人实测替换）</t>
+          <t>波次明细「实测清场」列</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
